--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,52 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102946521</v>
+        <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backen/Otto, Almnäs, Vg</t>
+          <t>Dicksonsdammen öster om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454006</v>
+        <v>453730</v>
       </c>
       <c r="R3" t="n">
-        <v>6458457</v>
+        <v>6458582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,81 +869,73 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ewa Lilliesköld</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ewa Lilliesköld</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102946521</t>
+          <t>https://artportalen.se/Sighting/137386061</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124407246</v>
+        <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>58439</v>
+        <v>93475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backen/Otto, Almnäs, Vg</t>
+          <t>Dicksonsdammen öster om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454006</v>
+        <v>453730</v>
       </c>
       <c r="R4" t="n">
-        <v>6458457</v>
+        <v>6458582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,55 +976,61 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ewa Lilliesköld</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ewa Lilliesköld</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124407246</t>
+          <t>https://artportalen.se/Sighting/137386062</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116003908</v>
+        <v>102946521</v>
       </c>
       <c r="B5" t="n">
-        <v>56837</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,8 +1040,6 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1108,27 +1077,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Funnen skadad på marken.</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1101,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,6 +1118,363 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102946521</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137386063</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93501</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>453730</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6458582</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386063</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124407246</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Backen/Otto, Almnäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>454006</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458457</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ewa Lilliesköld</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ewa Lilliesköld</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124407246</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116003908</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Backen/Otto, Almnäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>454006</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6458457</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Funnen skadad på marken.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ewa Lilliesköld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ewa Lilliesköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/116003908</t>
         </is>
@@ -1164,6 +1486,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137386063</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137386063</v>
       </c>
       <c r="B6" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137386063</v>
       </c>
       <c r="B6" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137386063</v>
       </c>
       <c r="B6" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39364-2026 artfynd.xlsx
+++ b/artfynd/A 39364-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386061</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386062</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137386063</v>
       </c>
       <c r="B6" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
